--- a/tame_output/ON/bt/strategyON_20230821.xlsx
+++ b/tame_output/ON/bt/strategyON_20230821.xlsx
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.6%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1695"/>
+  <dimension ref="A1:G1696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40495,7 +40495,7 @@
         <v>45157</v>
       </c>
       <c r="B1695" t="n">
-        <v>2.771280474719291</v>
+        <v>2.770291161535239</v>
       </c>
       <c r="C1695" t="n">
         <v>2.888074045681735</v>
@@ -40511,6 +40511,29 @@
       </c>
       <c r="G1695" t="n">
         <v>4.194900870641207</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="2" t="n">
+        <v>45158</v>
+      </c>
+      <c r="B1696" t="n">
+        <v>2.770362411625738</v>
+      </c>
+      <c r="C1696" t="n">
+        <v>2.890170122691142</v>
+      </c>
+      <c r="D1696" t="n">
+        <v>1.557667573281131</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>3.512880727689848</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>2.178044708265784</v>
+      </c>
+      <c r="G1696" t="n">
+        <v>4.196996947650614</v>
       </c>
     </row>
   </sheetData>
